--- a/LoanOfficer-A/2023/89 lukhamlu.xlsx
+++ b/LoanOfficer-A/2023/89 lukhamlu.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2100</v>
+        <v>5600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>9900</v>
+        <v>6400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -970,9 +970,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45316</v>
+      </c>
+      <c r="C6" s="4">
+        <v>700</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -996,9 +1002,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45316</v>
+      </c>
+      <c r="C7" s="4">
+        <v>700</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1022,9 +1034,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45316</v>
+      </c>
+      <c r="C8" s="4">
+        <v>700</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1048,9 +1066,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45316</v>
+      </c>
+      <c r="C9" s="4">
+        <v>700</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1074,9 +1098,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45316</v>
+      </c>
+      <c r="C10" s="4">
+        <v>700</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>

--- a/LoanOfficer-A/2023/89 lukhamlu.xlsx
+++ b/LoanOfficer-A/2023/89 lukhamlu.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5600</v>
+        <v>7000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>6400</v>
+        <v>5000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1130,9 +1130,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45337</v>
+      </c>
+      <c r="C11" s="4">
+        <v>700</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1156,9 +1162,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45337</v>
+      </c>
+      <c r="C12" s="4">
+        <v>700</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>

--- a/LoanOfficer-A/2023/89 lukhamlu.xlsx
+++ b/LoanOfficer-A/2023/89 lukhamlu.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7000</v>
+        <v>9800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5000</v>
+        <v>2200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1194,9 +1194,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45372</v>
+      </c>
+      <c r="C13" s="4">
+        <v>700</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1220,9 +1226,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45372</v>
+      </c>
+      <c r="C14" s="4">
+        <v>700</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1246,9 +1258,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45372</v>
+      </c>
+      <c r="C15" s="4">
+        <v>700</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1272,9 +1290,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45372</v>
+      </c>
+      <c r="C16" s="4">
+        <v>700</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
